--- a/outputs/tables/tabla_criterios_informacion.xlsx
+++ b/outputs/tables/tabla_criterios_informacion.xlsx
@@ -14,24 +14,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Criterio</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>Métrica</t>
   </si>
   <si>
     <t>Valor</t>
   </si>
   <si>
-    <t>WAIC</t>
-  </si>
-  <si>
-    <t>WAIC_se</t>
-  </si>
-  <si>
-    <t>LOO</t>
-  </si>
-  <si>
-    <t>LOO_se</t>
+    <t>ELPD_WAIC</t>
+  </si>
+  <si>
+    <t>ELPD_WAIC_SE</t>
+  </si>
+  <si>
+    <t>p_WAIC</t>
+  </si>
+  <si>
+    <t>ELPD_LOO</t>
+  </si>
+  <si>
+    <t>ELPD_LOO_SE</t>
+  </si>
+  <si>
+    <t>p_LOO</t>
+  </si>
+  <si>
+    <t>Divergencias_NUTS</t>
+  </si>
+  <si>
+    <t>R_hat_max</t>
+  </si>
+  <si>
+    <t>ESS_bulk_min</t>
+  </si>
+  <si>
+    <t>ESS_tail_min</t>
   </si>
 </sst>
 </file>
@@ -389,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -405,7 +423,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>4111.817210015797</v>
+        <v>-1296.488874796113</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -413,7 +431,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>97.13870142897947</v>
+        <v>25.62262168948308</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -421,7 +439,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>4312.981279049038</v>
+        <v>142.978850881702</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -429,7 +447,55 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>111.7692541991834</v>
+        <v>-1321.272312148847</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>26.73173442791879</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>167.762288234436</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>1.0175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>336.224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>352.6789</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_criterios_informacion.xlsx
+++ b/outputs/tables/tabla_criterios_informacion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Métrica</t>
   </si>
@@ -40,16 +40,13 @@
     <t>p_LOO</t>
   </si>
   <si>
-    <t>Divergencias_NUTS</t>
-  </si>
-  <si>
-    <t>R_hat_max</t>
-  </si>
-  <si>
-    <t>ESS_bulk_min</t>
-  </si>
-  <si>
-    <t>ESS_tail_min</t>
+    <t>Pareto_k_mayor_0.7</t>
+  </si>
+  <si>
+    <t>Pareto_k_0.5_a_0.7</t>
+  </si>
+  <si>
+    <t>Pareto_k_menor_0.5</t>
   </si>
 </sst>
 </file>
@@ -407,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -423,7 +420,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>-1296.488874796113</v>
+        <v>-1473.724258527367</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -431,7 +428,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>25.62262168948308</v>
+        <v>26.17493962971699</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -439,7 +436,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>142.978850881702</v>
+        <v>167.9849583339543</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -447,7 +444,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>-1321.272312148847</v>
+        <v>-1537.056294417802</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -455,7 +452,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>26.73173442791879</v>
+        <v>30.86485530288633</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -463,7 +460,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>167.762288234436</v>
+        <v>231.316994224389</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -471,7 +468,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -479,7 +476,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>1.0175</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -487,15 +484,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>336.224</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>352.6789</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_criterios_informacion.xlsx
+++ b/outputs/tables/tabla_criterios_informacion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Métrica</t>
   </si>
@@ -22,6 +22,15 @@
     <t>Valor</t>
   </si>
   <si>
+    <t>Modelo_Referencia</t>
+  </si>
+  <si>
+    <t>Metodo_Inferencia</t>
+  </si>
+  <si>
+    <t>Criterio_Convergencia</t>
+  </si>
+  <si>
     <t>ELPD_WAIC</t>
   </si>
   <si>
@@ -47,6 +56,15 @@
   </si>
   <si>
     <t>Pareto_k_menor_0.5</t>
+  </si>
+  <si>
+    <t>Modelo (c) Binomial Negativa (ICAR + No Estructurado) [Mejor LOO-CV]</t>
+  </si>
+  <si>
+    <t>ADVI (Adam lr=0.005)</t>
+  </si>
+  <si>
+    <t>Variación media móvil ELBO últimas 5,000 iteraciones &lt; 0.1%</t>
   </si>
 </sst>
 </file>
@@ -404,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -419,24 +437,24 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>-1473.724258527367</v>
+      <c r="B2" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>26.17493962971699</v>
+      <c r="B3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>167.9849583339543</v>
+      <c r="B4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -444,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>-1537.056294417802</v>
+        <v>-1219.559352321657</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -452,7 +470,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>30.86485530288633</v>
+        <v>25.82227081422354</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -460,7 +478,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>231.316994224389</v>
+        <v>103.4699346118752</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -468,7 +486,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>146</v>
+        <v>-1233.7458212532</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -476,7 +494,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>100</v>
+        <v>26.7589567450958</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -484,7 +502,31 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>242</v>
+        <v>117.6564035434187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>371</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_criterios_informacion.xlsx
+++ b/outputs/tables/tabla_criterios_informacion.xlsx
@@ -58,7 +58,7 @@
     <t>Pareto_k_menor_0.5</t>
   </si>
   <si>
-    <t>Modelo (c) Binomial Negativa (ICAR + No Estructurado) [Mejor LOO-CV]</t>
+    <t>Modelo (b) Binomial Negativa (ICAR) [Mejor LOO-CV]</t>
   </si>
   <si>
     <t>ADVI (Adam lr=0.005)</t>

--- a/outputs/tables/tabla_criterios_informacion.xlsx
+++ b/outputs/tables/tabla_criterios_informacion.xlsx
@@ -462,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>-1219.559352321657</v>
+        <v>-1219.559352321656</v>
       </c>
     </row>
     <row r="6" spans="1:2">
